--- a/data/processed/positivacao/2020-09_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2020-09_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -24217,7 +24217,7 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B919" t="inlineStr"/>
@@ -35465,7 +35465,7 @@
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1352" t="inlineStr"/>
@@ -64331,7 +64331,7 @@
     <row r="2463">
       <c r="A2463" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2463" t="inlineStr"/>
@@ -66002,12 +66002,12 @@
       <c r="A2528" t="inlineStr"/>
       <c r="B2528" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 0 cliente(s), não positivou 91 cliente(s) - Total vendido: R$ 0,00
+          <t>Vendedor 1 - VENDEDOR 01: positivou 0 cliente(s), não positivou 91 cliente(s) - Total vendido: R$ 0,00
 Vendedor 18 - LOJA: positivou 29 cliente(s), não positivou 789 cliente(s) - Total vendido: R$ 37.143,36
-Vendedor 3 - FERNANDA: positivou 21 cliente(s), não positivou 411 cliente(s) - Total vendido: R$ 16.800,17
-Vendedor 4 - DANIELA: positivou 0 cliente(s), não positivou 655 cliente(s) - Total vendido: R$ 0,00
+Vendedor 3 - VENDEDOR 03: positivou 21 cliente(s), não positivou 411 cliente(s) - Total vendido: R$ 16.800,17
+Vendedor 4 - VENDEDOR 04: positivou 0 cliente(s), não positivou 655 cliente(s) - Total vendido: R$ 0,00
 Vendedor 5 - SITE: positivou 0 cliente(s), não positivou 454 cliente(s) - Total vendido: R$ 0,00
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2528" t="inlineStr"/>
